--- a/static/format-upload/KAWI-import-mine-productions.xlsx
+++ b/static/format-upload/KAWI-import-mine-productions.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Desktop/import data/import/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/staticfiles/format-upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ACEC4D-547D-6349-9FA3-8AB4E03A8E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE47FF-FB27-4E40-92A8-45EE437251E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="34580" windowHeight="20940" tabRatio="527" xr2:uid="{CA29E963-52AE-4D69-A8ED-5318B4E42E2E}"/>
+    <workbookView xWindow="2660" yWindow="5720" windowWidth="34580" windowHeight="20940" tabRatio="527" xr2:uid="{CA29E963-52AE-4D69-A8ED-5318B4E42E2E}"/>
   </bookViews>
   <sheets>
     <sheet name="import-productions" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'import-productions'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'import-productions'!$A$1:$R$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{A320459A-1CEA-704D-A4B3-7986E2BD8BA2}">
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{A320459A-1CEA-704D-A4B3-7986E2BD8BA2}">
       <text>
         <r>
           <rPr>
@@ -167,9 +167,6 @@
     <t>Hauler</t>
   </si>
   <si>
-    <t>Hauler Class</t>
-  </si>
-  <si>
     <t>Loading Point</t>
   </si>
   <si>
@@ -203,12 +200,6 @@
     <t>Vendors</t>
   </si>
   <si>
-    <t>Sources</t>
-  </si>
-  <si>
-    <t>Dump Truck 30 Ton</t>
-  </si>
-  <si>
     <t>Pile Id</t>
   </si>
   <si>
@@ -218,12 +209,6 @@
     <t>NPM</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>OB</t>
-  </si>
-  <si>
     <t>DT-263</t>
   </si>
   <si>
@@ -233,16 +218,31 @@
     <t>Time Hauling</t>
   </si>
   <si>
-    <t>Workshop</t>
-  </si>
-  <si>
-    <t>Disposal</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>E-195</t>
+    <t>Parsing</t>
+  </si>
+  <si>
+    <t>Loader Class</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>E-180</t>
+  </si>
+  <si>
+    <t>PC 350</t>
+  </si>
+  <si>
+    <t>Pit Raja</t>
+  </si>
+  <si>
+    <t>All Area</t>
+  </si>
+  <si>
+    <t>Quarry</t>
+  </si>
+  <si>
+    <t>Mining</t>
   </si>
 </sst>
 </file>
@@ -391,7 +391,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -457,6 +457,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,121 +796,123 @@
     <col min="6" max="6" width="10.5" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125"/>
-    <col min="16" max="16" width="9.1640625" style="1"/>
-    <col min="17" max="17" width="8.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.83203125" style="9" customWidth="1"/>
-    <col min="19" max="19" width="14.5" style="9" customWidth="1"/>
+    <col min="9" max="9" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" style="1"/>
+    <col min="16" max="16" width="8.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.33203125" style="3" customWidth="1"/>
     <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="R1" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="15" t="s">
         <v>10</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
-        <v>45809</v>
+        <v>45886</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" s="17">
-        <v>0.6020833333333333</v>
+        <v>0.875</v>
       </c>
       <c r="E2" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="19">
+        <v>5</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="18"/>
+      <c r="L2" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="20"/>
-      <c r="I2" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="20"/>
-      <c r="L2" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
       <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="22">
-        <v>1</v>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="26">
+        <v>2</v>
       </c>
       <c r="S2" s="22"/>
     </row>
@@ -914,16 +925,16 @@
       <c r="F3" s="7"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="10"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="27"/>
       <c r="S3" s="8"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -935,16 +946,16 @@
       <c r="F4" s="19"/>
       <c r="G4" s="20"/>
       <c r="H4" s="20"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="18"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="20"/>
       <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
       <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="26"/>
       <c r="S4" s="22"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -956,16 +967,16 @@
       <c r="F5" s="7"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="10"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="27"/>
       <c r="S5" s="8"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -977,16 +988,16 @@
       <c r="F6" s="19"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="18"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
       <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="26"/>
       <c r="S6" s="22"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -998,16 +1009,16 @@
       <c r="F7" s="7"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="10"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="27"/>
       <c r="S7" s="8"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -1019,16 +1030,16 @@
       <c r="F8" s="19"/>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="18"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="20"/>
       <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
       <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="26"/>
       <c r="S8" s="22"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -1040,16 +1051,16 @@
       <c r="F9" s="7"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="10"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
       <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="27"/>
       <c r="S9" s="8"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -1061,16 +1072,16 @@
       <c r="F10" s="19"/>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="18"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="20"/>
       <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
       <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="26"/>
       <c r="S10" s="22"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -1082,16 +1093,16 @@
       <c r="F11" s="7"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="10"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
       <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="27"/>
       <c r="S11" s="8"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -1103,20 +1114,20 @@
       <c r="F12" s="19"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="18"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="20"/>
       <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
       <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="26"/>
       <c r="S12" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1" xr:uid="{4D3DC610-FF49-443E-8556-9D1E29AAC3E2}"/>
+  <autoFilter ref="A1:R1" xr:uid="{4D3DC610-FF49-443E-8556-9D1E29AAC3E2}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>

--- a/static/format-upload/KAWI-import-mine-productions.xlsx
+++ b/static/format-upload/KAWI-import-mine-productions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/staticfiles/format-upload/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/static/format-upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FE47FF-FB27-4E40-92A8-45EE437251E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F16220-D97F-284B-AB00-CE22AAFA7006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="5720" windowWidth="34580" windowHeight="20940" tabRatio="527" xr2:uid="{CA29E963-52AE-4D69-A8ED-5318B4E42E2E}"/>
+    <workbookView xWindow="1420" yWindow="1020" windowWidth="34580" windowHeight="20940" tabRatio="527" xr2:uid="{CA29E963-52AE-4D69-A8ED-5318B4E42E2E}"/>
   </bookViews>
   <sheets>
     <sheet name="import-productions" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Shift</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>Mining</t>
+  </si>
+  <si>
+    <t>Direct</t>
   </si>
 </sst>
 </file>
@@ -785,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3DC610-FF49-443E-8556-9D1E29AAC3E2}">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="1" customWidth="1"/>
@@ -806,11 +809,11 @@
     <col min="16" max="16" width="8.5" style="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="3"/>
+    <col min="19" max="20" width="11.33203125" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
@@ -866,10 +869,13 @@
         <v>17</v>
       </c>
       <c r="S1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="T1" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>45886</v>
       </c>
@@ -915,8 +921,9 @@
         <v>2</v>
       </c>
       <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="24"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -936,8 +943,9 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="27"/>
       <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -957,8 +965,9 @@
       <c r="Q4" s="22"/>
       <c r="R4" s="26"/>
       <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="24"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -978,8 +987,9 @@
       <c r="Q5" s="8"/>
       <c r="R5" s="27"/>
       <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="23"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
@@ -999,8 +1009,9 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="26"/>
       <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="24"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1020,8 +1031,9 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="27"/>
       <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -1041,8 +1053,9 @@
       <c r="Q8" s="22"/>
       <c r="R8" s="26"/>
       <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="24"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1062,8 +1075,9 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="27"/>
       <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="23"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -1083,8 +1097,9 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="26"/>
       <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="24"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1104,8 +1119,9 @@
       <c r="Q11" s="8"/>
       <c r="R11" s="27"/>
       <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="23"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1125,6 +1141,7 @@
       <c r="Q12" s="22"/>
       <c r="R12" s="26"/>
       <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{4D3DC610-FF49-443E-8556-9D1E29AAC3E2}"/>

--- a/static/format-upload/KAWI-import-mine-productions.xlsx
+++ b/static/format-upload/KAWI-import-mine-productions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meinardus/Project/python/mines-project/backend/static/format-upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F16220-D97F-284B-AB00-CE22AAFA7006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6AAD91-5E44-C147-8996-2E6C70A1166B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="1020" windowWidth="34580" windowHeight="20940" tabRatio="527" xr2:uid="{CA29E963-52AE-4D69-A8ED-5318B4E42E2E}"/>
   </bookViews>
@@ -394,7 +394,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -470,6 +470,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -808,8 +811,9 @@
     <col min="15" max="15" width="9.1640625" style="1"/>
     <col min="16" max="16" width="8.5" style="1" customWidth="1"/>
     <col min="17" max="17" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.33203125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.1640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.1640625" style="28" customWidth="1"/>
     <col min="21" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
@@ -868,10 +872,10 @@
       <c r="R1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="T1" s="25" t="s">
         <v>10</v>
       </c>
     </row>
@@ -920,8 +924,8 @@
       <c r="R2" s="26">
         <v>2</v>
       </c>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="24"/>
@@ -942,8 +946,8 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="8"/>
       <c r="R3" s="27"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
@@ -964,8 +968,8 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="22"/>
       <c r="R4" s="26"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="24"/>
@@ -986,8 +990,8 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="27"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="23"/>
@@ -1008,8 +1012,8 @@
       <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="26"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="24"/>
@@ -1030,8 +1034,8 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="27"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
@@ -1052,8 +1056,8 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="22"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="24"/>
@@ -1074,8 +1078,8 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="27"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="23"/>
@@ -1096,8 +1100,8 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="22"/>
       <c r="R10" s="26"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="24"/>
@@ -1118,8 +1122,8 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="27"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="23"/>
@@ -1140,8 +1144,8 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
       <c r="R12" s="26"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R1" xr:uid="{4D3DC610-FF49-443E-8556-9D1E29AAC3E2}"/>
